--- a/ksoft/docs/records/Import_Expense_Records_CD2565.xlsx
+++ b/ksoft/docs/records/Import_Expense_Records_CD2565.xlsx
@@ -1871,13 +1871,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E832218C-7631-4A43-931B-A12CC85CF0FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC3A549A-31EF-43E7-90B7-E9F5FBA9E949}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE8AC604-6616-47D0-8096-B0F490A1C0E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2DD777-CBCD-4B81-9DA3-82883E6FAA6D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{606259A3-4EBB-4B29-AD75-E81E9CDB572B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF78630B-D470-47EA-9797-0222A7288954}"/>
 </file>
--- a/ksoft/docs/records/Import_Expense_Records_CD2565.xlsx
+++ b/ksoft/docs/records/Import_Expense_Records_CD2565.xlsx
@@ -1871,13 +1871,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EC3A549A-31EF-43E7-90B7-E9F5FBA9E949}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E832218C-7631-4A43-931B-A12CC85CF0FB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0F2DD777-CBCD-4B81-9DA3-82883E6FAA6D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE8AC604-6616-47D0-8096-B0F490A1C0E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF78630B-D470-47EA-9797-0222A7288954}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{606259A3-4EBB-4B29-AD75-E81E9CDB572B}"/>
 </file>